--- a/data/trending_integrated_20261012_11.xlsx
+++ b/data/trending_integrated_20261012_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
         <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19709309220</v>
+        <v>19723640420</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>130792940090</v>
+        <v>131070980810</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -711,7 +711,7 @@
         <v>465</v>
       </c>
       <c r="R3" t="n">
-        <v>-102000</v>
+        <v>15000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13600</v>
+        <v>13770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+22.08%</t>
+          <t>'+23.61%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
         <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>137357521080</v>
+        <v>139363965835</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -803,23 +803,23 @@
         <v>3200</v>
       </c>
       <c r="R4" t="n">
-        <v>-414000</v>
+        <v>-487000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자체 개발 특허 출원 발표, 긍정적 기대감 형성. 거래량 동반 상승세 지속 여부 관건.</t>
+          <t>특허 출원 등 긍정적 소식에도 불구하고 외국인, 기관 매도세 관찰. 상승세 지속 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특허 출원', '거래량', '상승세']</t>
+          <t>['특허', '매도세', '상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.80%</t>
+          <t>'+16.44%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
         <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>9514882832</v>
+        <v>9635167560</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -895,7 +895,7 @@
         <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>-108000</v>
+        <v>-270000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7900</v>
+        <v>7880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.58%</t>
+          <t>'+11.30%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -969,7 +969,7 @@
         <v>6830</v>
       </c>
       <c r="L6" t="n">
-        <v>7950</v>
+        <v>8090</v>
       </c>
       <c r="M6" t="n">
         <v>6720</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>48724017115</v>
+        <v>62192791170</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -987,10 +987,10 @@
         <v>2890</v>
       </c>
       <c r="R6" t="n">
-        <v>44000</v>
+        <v>-136000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14380</v>
+        <v>14360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.38%</t>
+          <t>'+3.24%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>94636174410</v>
+        <v>96720941130</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1079,23 +1079,23 @@
         <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>85000</v>
+        <v>-3000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 방산주 상승에도 불구하고 주가 흐름에 대한 불확실성 언급. 보호예수 해제 및 투매 가능성에 대한 우려와 개인 매수세 주목.</t>
+          <t>보호예수 해제 및 투매 우려 속에서 상승 기대감 언급. 방산, 우주 테마 관련 소식 포함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산주', '보호예수', '주가 흐름']</t>
+          <t>['보호예수', '방산', '우주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11470</v>
+        <v>11460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.15%</t>
+          <t>'+1.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
         <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H8" t="n">
         <v>0.41</v>
@@ -1162,7 +1162,7 @@
         <v>0.44</v>
       </c>
       <c r="O8" t="n">
-        <v>24218475910</v>
+        <v>24750032165</v>
       </c>
       <c r="P8" t="n">
         <v>29750</v>
@@ -1171,7 +1171,7 @@
         <v>11120</v>
       </c>
       <c r="R8" t="n">
-        <v>56000</v>
+        <v>46000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45250</v>
+        <v>44900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.88%</t>
+          <t>'-1.64%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F9" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G9" t="n">
-        <v>2028</v>
+        <v>2077</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>29613532550</v>
+        <v>30106287400</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1263,7 +1263,7 @@
         <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-128000</v>
+        <v>-115000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>258750</v>
+        <v>256500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.24%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="G10" t="n">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="H10" t="n">
         <v>46.35</v>
@@ -1346,7 +1346,7 @@
         <v>46.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1604581537250</v>
+        <v>1673444548500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1355,23 +1355,23 @@
         <v>90200</v>
       </c>
       <c r="R10" t="n">
-        <v>-171000</v>
+        <v>-416000</v>
       </c>
       <c r="S10" t="n">
-        <v>90000</v>
+        <v>-81000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>영업이익 규모에 비해 부진한 주가에 대한 불만과 정치적 이슈 언급. 외국인 투자자 이탈 및 한국 증시 전반의 부진 지적.</t>
+          <t>역대급 실적 발표 의혹 및 국내 증시 부진에 대한 부정적 언급. 투자처 해외 이전 필요성 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '주가부양', '외국인']</t>
+          <t>['실적', '부진', '해외']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4190</v>
+        <v>4140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-3.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-2.94</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
@@ -1438,7 +1438,7 @@
         <v>4.46</v>
       </c>
       <c r="O11" t="n">
-        <v>14572305716</v>
+        <v>15125666456</v>
       </c>
       <c r="P11" t="n">
         <v>5470</v>
@@ -1447,7 +1447,7 @@
         <v>2810</v>
       </c>
       <c r="R11" t="n">
-        <v>-35000</v>
+        <v>-92000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2245</v>
+        <v>16150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>67</v>
+        <v>381</v>
       </c>
       <c r="H12" t="n">
-        <v>1.48</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2305</v>
+        <v>16670</v>
       </c>
       <c r="K12" t="n">
-        <v>2430</v>
+        <v>16500</v>
       </c>
       <c r="L12" t="n">
-        <v>2445</v>
+        <v>16870</v>
       </c>
       <c r="M12" t="n">
-        <v>2210</v>
+        <v>16150</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>27797583421</v>
+        <v>33654847020</v>
       </c>
       <c r="P12" t="n">
-        <v>2465</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>865</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-316000</v>
+        <v>367000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
+          <t>주주 연대의 활동 언급 및 '뱅크런' 등 부정적 용어 반복 사용. 목표가 3만원 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,20 +1555,20 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
+          <t>['주주연대', '뱅크런', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1637000</v>
+        <v>1625000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G13" t="n">
-        <v>1586</v>
+        <v>1644</v>
       </c>
       <c r="H13" t="n">
         <v>49.52</v>
@@ -1622,7 +1622,7 @@
         <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>2021826116500</v>
+        <v>2099718859500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1631,23 +1631,23 @@
         <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>-217000</v>
+        <v>-276000</v>
       </c>
       <c r="S13" t="n">
-        <v>44000</v>
+        <v>14000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관 지어 주가 하락을 비판. 솔리다임 중복 상장 논란 및 주주 가치 훼손에 대한 불만 표출.</t>
+          <t>자회사 상장 논란 및 정치적 이슈와 연관된 부정적 언급. 주가 하락 및 투자 가치 훼손 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 하락', '중복 상장', '주주 가치']</t>
+          <t>['자회사', '상장', '가치']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16230</v>
+        <v>18230</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.64%</t>
+          <t>'-3.34%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>377</v>
+        <v>241</v>
       </c>
       <c r="H14" t="n">
-        <v>9.470000000000001</v>
+        <v>27.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16670</v>
+        <v>18860</v>
       </c>
       <c r="K14" t="n">
-        <v>16500</v>
+        <v>18690</v>
       </c>
       <c r="L14" t="n">
-        <v>16870</v>
+        <v>18760</v>
       </c>
       <c r="M14" t="n">
-        <v>16220</v>
+        <v>18100</v>
       </c>
       <c r="N14" t="n">
-        <v>9.460000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>31374867575</v>
+        <v>26402815985</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>18100</v>
       </c>
       <c r="R14" t="n">
-        <v>221000</v>
+        <v>29000</v>
       </c>
       <c r="S14" t="n">
-        <v>11000</v>
+        <v>23000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대규모 공매도 및 뱅크런에 대한 의혹 제기와 주가 조작 가능성 주장. 소액주주 연대의 적극적인 행동 촉구.</t>
+          <t>조선주 순환매 기대에도 불구하고 부진한 주가에 대한 실망감 표출. 원전 사업 부진과 공매도 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '뱅크런', '소액주주']</t>
+          <t>['조선주', '순환매', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,99 +1752,99 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18290</v>
+        <v>2215</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.02%</t>
+          <t>'-3.90%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>235</v>
+        <v>67</v>
       </c>
       <c r="H15" t="n">
-        <v>27.61</v>
+        <v>1.48</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18860</v>
+        <v>2305</v>
       </c>
       <c r="K15" t="n">
-        <v>18690</v>
+        <v>2430</v>
       </c>
       <c r="L15" t="n">
-        <v>18760</v>
+        <v>2445</v>
       </c>
       <c r="M15" t="n">
-        <v>18100</v>
+        <v>2210</v>
       </c>
       <c r="N15" t="n">
-        <v>27.68</v>
+        <v>1.32</v>
       </c>
       <c r="O15" t="n">
-        <v>25690282810</v>
+        <v>28113990093</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>2465</v>
       </c>
       <c r="Q15" t="n">
-        <v>18100</v>
+        <v>865</v>
       </c>
       <c r="R15" t="n">
-        <v>25000</v>
+        <v>-442000</v>
       </c>
       <c r="S15" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>조선주 순환매 기대에도 불구하고 부진한 주가에 대한 실망감 표출. 원전 사업 부진과 공매도 가능성 언급.</t>
+          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['조선주', '순환매', '공매도']</t>
+          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7810</v>
+        <v>7760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.29%</t>
+          <t>'-4.90%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1892,29 +1892,29 @@
         <v>8110</v>
       </c>
       <c r="M16" t="n">
-        <v>7800</v>
+        <v>7760</v>
       </c>
       <c r="N16" t="n">
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>12602961415</v>
+        <v>14658512400</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>7800</v>
+        <v>7760</v>
       </c>
       <c r="R16" t="n">
-        <v>-299000</v>
+        <v>-595000</v>
       </c>
       <c r="S16" t="n">
-        <v>-2000</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>장기간의 주가 부진과 악재성 뉴스에 대한 불만 토로. 유상증자 및 상장폐지 가능성 언급하며 투자 심리 위축.</t>
+          <t>악의적 뉴스, 목표가 하향, 차트 회복 불능 등 부정적 전망. 개인 매수 지속 및 유상증자 가능성 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가 부진', '악재', '유상증자']</t>
+          <t>['뉴스', '목표가', '유상증자']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16010</v>
+        <v>15890</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.66%</t>
+          <t>'-6.36%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G17" t="n">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>60148515925</v>
+        <v>61778574965</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -1999,23 +1999,23 @@
         <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-29000</v>
+        <v>59000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>광통신 테마 상승 기대와 달리 급락하는 주가에 대한 불만. 공매도 규제 및 투경 효과 미미 지적.</t>
+          <t>광통신 시장 성장률 및 AI 관련 긍정적 뉴스 언급에도 불구하고 주가 하락 및 공매도 관련 부정적 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '테마', '공매도']</t>
+          <t>['광통신', 'AI', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26350</v>
+        <v>26150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.23%</t>
+          <t>'-6.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>36734614975</v>
+        <v>38552244900</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2091,10 +2091,10 @@
         <v>15960</v>
       </c>
       <c r="R18" t="n">
-        <v>-24000</v>
+        <v>-9000</v>
       </c>
       <c r="S18" t="n">
-        <v>2000</v>
+        <v>-2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261012_11.xlsx
+++ b/data/trending_integrated_20261012_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19723640420</v>
+        <v>19737694460</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131070980810</v>
+        <v>131145183020</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -762,13 +762,13 @@
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>139363965835</v>
+        <v>140883438575</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>특허 출원 등 긍정적 소식에도 불구하고 외국인, 기관 매도세 관찰. 상승세 지속 가능성 언급.</t>
+          <t>금호건설의 특허 출원과 상승세 지속 전망. 다만 외인, 기관, 기타법인의 매도세가 감지됨.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특허', '매도세', '상승']</t>
+          <t>['특허 출원', '상승세', '매도세']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.44%</t>
+          <t>'+16.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>9635167560</v>
+        <v>9852157266</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7880</v>
+        <v>7870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.30%</t>
+          <t>'+11.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>62192791170</v>
+        <v>70943092695</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14360</v>
+        <v>14340</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.24%</t>
+          <t>'+3.09%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>96720941130</v>
+        <v>99667190200</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11460</v>
+        <v>11330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.06%</t>
+          <t>'-0.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H8" t="n">
         <v>0.41</v>
@@ -1162,7 +1162,7 @@
         <v>0.44</v>
       </c>
       <c r="O8" t="n">
-        <v>24750032165</v>
+        <v>25163057275</v>
       </c>
       <c r="P8" t="n">
         <v>29750</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44900</v>
+        <v>44950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.64%</t>
+          <t>'-1.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F9" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G9" t="n">
-        <v>2077</v>
+        <v>2119</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>30106287400</v>
+        <v>30462526225</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>256500</v>
+        <v>256750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-2.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G10" t="n">
-        <v>1546</v>
+        <v>1549</v>
       </c>
       <c r="H10" t="n">
         <v>46.35</v>
@@ -1346,7 +1346,7 @@
         <v>46.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1673444548500</v>
+        <v>1718683102500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>역대급 실적 발표 의혹 및 국내 증시 부진에 대한 부정적 언급. 투자처 해외 이전 필요성 제기.</t>
+          <t>삼성전자의 역대급 실적에도 불구하고 주가 부양이 이루어지지 않는 상황에 대한 불만. 한국 증시의 전반적인 부진이 언급됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', '부진', '해외']</t>
+          <t>['영업이익', '주가 부양', '한국 증시']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4140</v>
+        <v>16190</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'-2.88%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-2.94</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>54</v>
+        <v>414</v>
       </c>
       <c r="H11" t="n">
-        <v>1.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4270</v>
+        <v>16670</v>
       </c>
       <c r="K11" t="n">
-        <v>4150</v>
+        <v>16500</v>
       </c>
       <c r="L11" t="n">
-        <v>4495</v>
+        <v>16870</v>
       </c>
       <c r="M11" t="n">
-        <v>4090</v>
+        <v>16130</v>
       </c>
       <c r="N11" t="n">
-        <v>4.46</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>15125666456</v>
+        <v>34861908445</v>
       </c>
       <c r="P11" t="n">
-        <v>5470</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>2810</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-92000</v>
+        <v>367000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
+          <t>주주 연대의 활동 언급 및 '뱅크런' 등 부정적 용어 반복 사용. 목표가 3만원 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,51 +1463,51 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['코로나19', '모더나', '단기 모멘텀']</t>
+          <t>['주주연대', '뱅크런', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16150</v>
+        <v>1630000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>493</v>
       </c>
       <c r="G12" t="n">
-        <v>381</v>
+        <v>1650</v>
       </c>
       <c r="H12" t="n">
-        <v>9.470000000000001</v>
+        <v>49.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16670</v>
+        <v>1681000</v>
       </c>
       <c r="K12" t="n">
-        <v>16500</v>
+        <v>1640000</v>
       </c>
       <c r="L12" t="n">
-        <v>16870</v>
+        <v>1653000</v>
       </c>
       <c r="M12" t="n">
-        <v>16150</v>
+        <v>1605000</v>
       </c>
       <c r="N12" t="n">
-        <v>9.460000000000001</v>
+        <v>49.59</v>
       </c>
       <c r="O12" t="n">
-        <v>33654847020</v>
+        <v>2162601305500</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>367000</v>
+        <v>-276000</v>
       </c>
       <c r="S12" t="n">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주주 연대의 활동 언급 및 '뱅크런' 등 부정적 용어 반복 사용. 목표가 3만원 언급.</t>
+          <t>SK하이닉스의 주가 하락에 대한 정치적 책임론과 자회사 상장 논란. 솔리다임 중복 상장으로 인한 주주 가치 훼손 우려가 제기됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주주연대', '뱅크런', '목표가']</t>
+          <t>['주가 하락', '자회사 상장', '주주 가치']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1625000</v>
+        <v>2230</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
-        <v>484</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>1644</v>
+        <v>67</v>
       </c>
       <c r="H13" t="n">
-        <v>49.52</v>
+        <v>1.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1681000</v>
+        <v>2305</v>
       </c>
       <c r="K13" t="n">
-        <v>1640000</v>
+        <v>2430</v>
       </c>
       <c r="L13" t="n">
-        <v>1653000</v>
+        <v>2445</v>
       </c>
       <c r="M13" t="n">
-        <v>1605000</v>
+        <v>2210</v>
       </c>
       <c r="N13" t="n">
-        <v>49.59</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2099718859500</v>
+        <v>28300352365</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>2465</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>865</v>
       </c>
       <c r="R13" t="n">
-        <v>-276000</v>
+        <v>-442000</v>
       </c>
       <c r="S13" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자회사 상장 논란 및 정치적 이슈와 연관된 부정적 언급. 주가 하락 및 투자 가치 훼손 우려.</t>
+          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자회사', '상장', '가치']</t>
+          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18230</v>
+        <v>18240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.34%</t>
+          <t>'-3.29%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
         <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="H14" t="n">
         <v>27.61</v>
@@ -1714,7 +1714,7 @@
         <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>26402815985</v>
+        <v>26884891790</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>조선주 순환매 기대에도 불구하고 부진한 주가에 대한 실망감 표출. 원전 사업 부진과 공매도 가능성 언급.</t>
+          <t>삼성중공업의 LNG·FLNG '쌍끌이 수주' 랠리에도 불구하고 주가 하락에 대한 우려. 조선주 순환매 및 국장 전반의 혼란이 언급됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '순환매', '공매도']</t>
+          <t>['쌍끌이 수주', '주가 하락', '조선주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,123 +1759,123 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2215</v>
+        <v>7760</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.90%</t>
+          <t>'-4.90%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="G15" t="n">
-        <v>67</v>
+        <v>466</v>
       </c>
       <c r="H15" t="n">
-        <v>1.48</v>
+        <v>26.37</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2305</v>
+        <v>8160</v>
       </c>
       <c r="K15" t="n">
-        <v>2430</v>
+        <v>8070</v>
       </c>
       <c r="L15" t="n">
-        <v>2445</v>
+        <v>8110</v>
       </c>
       <c r="M15" t="n">
-        <v>2210</v>
+        <v>7730</v>
       </c>
       <c r="N15" t="n">
-        <v>1.32</v>
+        <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>28113990093</v>
+        <v>15547948215</v>
       </c>
       <c r="P15" t="n">
-        <v>2465</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>865</v>
+        <v>7730</v>
       </c>
       <c r="R15" t="n">
-        <v>-442000</v>
+        <v>-595000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
+          <t>LG디스플레이의 지속적인 주가 하락과 투자자들의 절망적인 심리. FLiPP 기술 관련 언급과 3분기 영업이익 발표가 혼재됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
+          <t>['주가 하락', '절망', '영업이익']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7760</v>
+        <v>4010</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.90%</t>
+          <t>'-6.09%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.01</v>
+        <v>-2.94</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>433</v>
+        <v>55</v>
       </c>
       <c r="H16" t="n">
-        <v>26.37</v>
+        <v>1.52</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8160</v>
+        <v>4270</v>
       </c>
       <c r="K16" t="n">
-        <v>8070</v>
+        <v>4150</v>
       </c>
       <c r="L16" t="n">
-        <v>8110</v>
+        <v>4495</v>
       </c>
       <c r="M16" t="n">
-        <v>7760</v>
+        <v>4005</v>
       </c>
       <c r="N16" t="n">
-        <v>26.38</v>
+        <v>4.46</v>
       </c>
       <c r="O16" t="n">
-        <v>14658512400</v>
+        <v>15719381866</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>5470</v>
       </c>
       <c r="Q16" t="n">
-        <v>7760</v>
+        <v>2810</v>
       </c>
       <c r="R16" t="n">
-        <v>-595000</v>
+        <v>-92000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>악의적 뉴스, 목표가 하향, 차트 회복 불능 등 부정적 전망. 개인 매수 지속 및 유상증자 가능성 제기.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['뉴스', '목표가', '유상증자']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15890</v>
+        <v>15910</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.36%</t>
+          <t>'-6.25%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F17" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>61778574965</v>
+        <v>62962534670</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>광통신 시장 성장률 및 AI 관련 긍정적 뉴스 언급에도 불구하고 주가 하락 및 공매도 관련 부정적 전망.</t>
+          <t>대한광통신의 광통신 테마 부각과 10월 3만원 예상. 하지만 급락 후 오후 급상승 가능성에 대한 기대와 함께 투기적 흐름이 감지됨.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '공매도']</t>
+          <t>['광통신 테마', '급상승', '투기']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>38552244900</v>
+        <v>39683816950</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>

--- a/data/trending_integrated_20261012_11.xlsx
+++ b/data/trending_integrated_20261012_11.xlsx
@@ -584,7 +584,7 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19737694460</v>
+        <v>19799203700</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131145183020</v>
+        <v>131244624830</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13770</v>
+        <v>13790</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.61%</t>
+          <t>'+23.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>140883438575</v>
+        <v>141924361765</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금호건설의 특허 출원과 상승세 지속 전망. 다만 외인, 기관, 기타법인의 매도세가 감지됨.</t>
+          <t>자체 개발 특허 출원으로 상승 기대감 있으나, 외인·기관·기타법인 매도세와 함께 상한가 진입 실패 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특허 출원', '상승세', '매도세']</t>
+          <t>['특허 출원', '매도세', '상한가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.22%</t>
+          <t>'+16.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>9852157266</v>
+        <v>10005551825</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7870</v>
+        <v>7920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.16%</t>
+          <t>'+11.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -969,7 +969,7 @@
         <v>6830</v>
       </c>
       <c r="L6" t="n">
-        <v>8090</v>
+        <v>8100</v>
       </c>
       <c r="M6" t="n">
         <v>6720</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>70943092695</v>
+        <v>78133058265</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14340</v>
+        <v>14390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.09%</t>
+          <t>'+3.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>99667190200</v>
+        <v>100929162445</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보호예수 해제 및 투매 우려 속에서 상승 기대감 언급. 방산, 우주 테마 관련 소식 포함.</t>
+          <t>미국 방산주 상승에 따른 기대감 속에서 보호예수 해제 및 세력 작전에 대한 경계심 공존.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보호예수', '방산', '우주']</t>
+          <t>['방산주', '보호예수', '세력 작전']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11330</v>
+        <v>11250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.09%</t>
+          <t>'-0.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
         <v>0.41</v>
@@ -1162,7 +1162,7 @@
         <v>0.44</v>
       </c>
       <c r="O8" t="n">
-        <v>25163057275</v>
+        <v>25663286145</v>
       </c>
       <c r="P8" t="n">
         <v>29750</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44950</v>
+        <v>45150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.53%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F9" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G9" t="n">
-        <v>2119</v>
+        <v>2176</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>30462526225</v>
+        <v>30829490825</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>256750</v>
+        <v>257250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.00%</t>
+          <t>'-1.81%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G10" t="n">
-        <v>1549</v>
+        <v>1574</v>
       </c>
       <c r="H10" t="n">
         <v>46.35</v>
@@ -1346,7 +1346,7 @@
         <v>46.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1718683102500</v>
+        <v>1765543195750</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성전자의 역대급 실적에도 불구하고 주가 부양이 이루어지지 않는 상황에 대한 불만. 한국 증시의 전반적인 부진이 언급됨.</t>
+          <t>역대급 실적 발표에도 불구하고 주가 부양 실패 및 한국 증시 하락세에 대한 답답함 표출. 미국 이전 희망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '한국 증시']</t>
+          <t>['영업이익', '실적 발표', '한국 증시']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16190</v>
+        <v>1638000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.88%</t>
+          <t>'-2.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>499</v>
       </c>
       <c r="G11" t="n">
-        <v>414</v>
+        <v>1727</v>
       </c>
       <c r="H11" t="n">
-        <v>9.470000000000001</v>
+        <v>49.52</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16670</v>
+        <v>1681000</v>
       </c>
       <c r="K11" t="n">
-        <v>16500</v>
+        <v>1640000</v>
       </c>
       <c r="L11" t="n">
-        <v>16870</v>
+        <v>1653000</v>
       </c>
       <c r="M11" t="n">
-        <v>16130</v>
+        <v>1605000</v>
       </c>
       <c r="N11" t="n">
-        <v>9.460000000000001</v>
+        <v>49.59</v>
       </c>
       <c r="O11" t="n">
-        <v>34861908445</v>
+        <v>2227327980000</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>403000</v>
       </c>
       <c r="R11" t="n">
-        <v>367000</v>
+        <v>-276000</v>
       </c>
       <c r="S11" t="n">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주주 연대의 활동 언급 및 '뱅크런' 등 부정적 용어 반복 사용. 목표가 3만원 언급.</t>
+          <t>자회사 상장(쪼개기 상장) 논란 및 정치적 이슈와 연관된 주가 하락에 대한 불만 고조.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주주연대', '뱅크런', '목표가']</t>
+          <t>['쪼개기 상장', '자회사 상장', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1630000</v>
+        <v>16200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>109</v>
       </c>
       <c r="F12" t="n">
-        <v>493</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>1650</v>
+        <v>425</v>
       </c>
       <c r="H12" t="n">
-        <v>49.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1681000</v>
+        <v>16670</v>
       </c>
       <c r="K12" t="n">
-        <v>1640000</v>
+        <v>16500</v>
       </c>
       <c r="L12" t="n">
-        <v>1653000</v>
+        <v>16870</v>
       </c>
       <c r="M12" t="n">
-        <v>1605000</v>
+        <v>16130</v>
       </c>
       <c r="N12" t="n">
-        <v>49.59</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>2162601305500</v>
+        <v>35995005100</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-276000</v>
+        <v>367000</v>
       </c>
       <c r="S12" t="n">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>SK하이닉스의 주가 하락에 대한 정치적 책임론과 자회사 상장 논란. 솔리다임 중복 상장으로 인한 주주 가치 훼손 우려가 제기됨.</t>
+          <t>주주 연대의 활동 언급 및 '뱅크런' 등 부정적 용어 반복 사용. 목표가 3만원 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 하락', '자회사 상장', '주주 가치']</t>
+          <t>['주주연대', '뱅크런', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,191 +1568,191 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2230</v>
+        <v>18270</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>67</v>
+        <v>263</v>
       </c>
       <c r="H13" t="n">
-        <v>1.48</v>
+        <v>27.61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2305</v>
+        <v>18860</v>
       </c>
       <c r="K13" t="n">
-        <v>2430</v>
+        <v>18690</v>
       </c>
       <c r="L13" t="n">
-        <v>2445</v>
+        <v>18760</v>
       </c>
       <c r="M13" t="n">
-        <v>2210</v>
+        <v>18100</v>
       </c>
       <c r="N13" t="n">
-        <v>1.32</v>
+        <v>27.68</v>
       </c>
       <c r="O13" t="n">
-        <v>28300352365</v>
+        <v>27681243235</v>
       </c>
       <c r="P13" t="n">
-        <v>2465</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>865</v>
+        <v>18100</v>
       </c>
       <c r="R13" t="n">
-        <v>-442000</v>
+        <v>29000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
+          <t>LNG·FLNG '쌍끌이 수주' 소식에도 불구하고 주가 하락 지속. 공매도 및 노조 문제 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
+          <t>['수주 랠리', '공매도', '노조']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18240</v>
+        <v>2225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.29%</t>
+          <t>'-3.47%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>269</v>
+        <v>89</v>
       </c>
       <c r="H14" t="n">
-        <v>27.61</v>
+        <v>1.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18860</v>
+        <v>2305</v>
       </c>
       <c r="K14" t="n">
-        <v>18690</v>
+        <v>2430</v>
       </c>
       <c r="L14" t="n">
-        <v>18760</v>
+        <v>2445</v>
       </c>
       <c r="M14" t="n">
-        <v>18100</v>
+        <v>2210</v>
       </c>
       <c r="N14" t="n">
-        <v>27.68</v>
+        <v>1.32</v>
       </c>
       <c r="O14" t="n">
-        <v>26884891790</v>
+        <v>28415369365</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>2465</v>
       </c>
       <c r="Q14" t="n">
-        <v>18100</v>
+        <v>865</v>
       </c>
       <c r="R14" t="n">
-        <v>29000</v>
+        <v>-442000</v>
       </c>
       <c r="S14" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성중공업의 LNG·FLNG '쌍끌이 수주' 랠리에도 불구하고 주가 하락에 대한 우려. 조선주 순환매 및 국장 전반의 혼란이 언급됨.</t>
+          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['쌍끌이 수주', '주가 하락', '조선주']</t>
+          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7760</v>
+        <v>7780</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.90%</t>
+          <t>'-4.66%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="H15" t="n">
         <v>26.37</v>
@@ -1806,7 +1806,7 @@
         <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>15547948215</v>
+        <v>15956456440</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>LG디스플레이의 지속적인 주가 하락과 투자자들의 절망적인 심리. FLiPP 기술 관련 언급과 3분기 영업이익 발표가 혼재됨.</t>
+          <t>수년간의 악재와 부정적 전망 속에서 개인 매수세만 유지. 유상증자 및 상폐 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 하락', '절망', '영업이익']</t>
+          <t>['유상증자', '상폐', '개인 매수세']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,215 +1851,215 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4010</v>
+        <v>16000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.09%</t>
+          <t>'-5.72%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.94</v>
+        <v>-0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>55</v>
+        <v>398</v>
       </c>
       <c r="H16" t="n">
-        <v>1.52</v>
+        <v>3.37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4270</v>
+        <v>16970</v>
       </c>
       <c r="K16" t="n">
-        <v>4150</v>
+        <v>17030</v>
       </c>
       <c r="L16" t="n">
-        <v>4495</v>
+        <v>17400</v>
       </c>
       <c r="M16" t="n">
-        <v>4005</v>
+        <v>15650</v>
       </c>
       <c r="N16" t="n">
-        <v>4.46</v>
+        <v>3.97</v>
       </c>
       <c r="O16" t="n">
-        <v>15719381866</v>
+        <v>63960047610</v>
       </c>
       <c r="P16" t="n">
-        <v>5470</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>2810</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-92000</v>
+        <v>59000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
+          <t>대한광통신의 광통신 테마 부각과 10월 3만원 예상. 하지만 급락 후 오후 급상승 가능성에 대한 기대와 함께 투기적 흐름이 감지됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['코로나19', '모더나', '단기 모멘텀']</t>
+          <t>['광통신 테마', '급상승', '투기']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15910</v>
+        <v>26350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.25%</t>
+          <t>'-6.23%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.6</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>389</v>
+        <v>54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.37</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16970</v>
+        <v>28100</v>
       </c>
       <c r="K17" t="n">
-        <v>17030</v>
+        <v>27600</v>
       </c>
       <c r="L17" t="n">
-        <v>17400</v>
+        <v>27800</v>
       </c>
       <c r="M17" t="n">
-        <v>15650</v>
+        <v>26050</v>
       </c>
       <c r="N17" t="n">
-        <v>3.97</v>
+        <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>62962534670</v>
+        <v>40394648150</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>15960</v>
       </c>
       <c r="R17" t="n">
-        <v>59000</v>
+        <v>-9000</v>
       </c>
       <c r="S17" t="n">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대한광통신의 광통신 테마 부각과 10월 3만원 예상. 하지만 급락 후 오후 급상승 가능성에 대한 기대와 함께 투기적 흐름이 감지됨.</t>
+          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신 테마', '급상승', '투기']</t>
+          <t>['경영진 부진', '기술유출', '실적 우려']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26150</v>
+        <v>3965</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.94%</t>
+          <t>'-7.14%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.94</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H18" t="n">
-        <v>9.460000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>28100</v>
+        <v>4270</v>
       </c>
       <c r="K18" t="n">
-        <v>27600</v>
+        <v>4150</v>
       </c>
       <c r="L18" t="n">
-        <v>27800</v>
+        <v>4495</v>
       </c>
       <c r="M18" t="n">
-        <v>26050</v>
+        <v>3950</v>
       </c>
       <c r="N18" t="n">
-        <v>10.02</v>
+        <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>39683816950</v>
+        <v>16168437136</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>5470</v>
       </c>
       <c r="Q18" t="n">
-        <v>15960</v>
+        <v>2810</v>
       </c>
       <c r="R18" t="n">
-        <v>-9000</v>
+        <v>-92000</v>
       </c>
       <c r="S18" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['경영진 부진', '기술유출', '실적 우려']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>002720</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261012_11.xlsx
+++ b/data/trending_integrated_20261012_11.xlsx
@@ -581,10 +581,10 @@
         <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19799203700</v>
+        <v>19808390540</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131244624830</v>
+        <v>131398763510</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13790</v>
+        <v>13750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.79%</t>
+          <t>'+23.43%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F4" t="n">
         <v>68</v>
       </c>
       <c r="G4" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>141924361765</v>
+        <v>143539821205</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자체 개발 특허 출원으로 상승 기대감 있으나, 외인·기관·기타법인 매도세와 함께 상한가 진입 실패 전망.</t>
+          <t>자체 개발 특허 출원 소식 있으나, 외인/기관/기타법인 매도세로 인한 상승 모멘텀 약화. 개미 꼬시기 의혹 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특허 출원', '매도세', '상한가']</t>
+          <t>['특허 출원', '매도세', '개미 꼬시기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1617</v>
+        <v>1624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.58%</t>
+          <t>'+17.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10005551825</v>
+        <v>10090890037</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -946,13 +946,13 @@
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>78133058265</v>
+        <v>81178793505</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>부동산 테마주로서 수도권 거점 공장을 보유하며, 10월 12일 성수 메가 프로젝트와 연관된 기대감이 있으나, 일부 매도 물량과 AI 관련 부정적 전망도 존재.</t>
+          <t>성수메가프로젝트 및 건설기초소재 대장주로서의 입지 강조. 불황 속 226억 투자 및 반도체 수요 겨냥. 공매도 쇼퀴즈 및 국토부 승인 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['부동산 테마주', '거점 공장', 'AI 전망']</t>
+          <t>['건설기초소재', '반도체 수요', '공매도 쇼퀴즈']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14390</v>
+        <v>14630</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.45%</t>
+          <t>'+5.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>100929162445</v>
+        <v>103463676600</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 방산주 상승에 따른 기대감 속에서 보호예수 해제 및 세력 작전에 대한 경계심 공존.</t>
+          <t>방산·우주 테마 기대감 속에 '상' 냄새 언급. 보호예수 해제 및 대차거래 관련 리스크 존재. 단기 슈팅 및 개미 꼬시기 의혹.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산주', '보호예수', '세력 작전']</t>
+          <t>['방산 테마', '우주 테마', '보호예수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11250</v>
+        <v>11325</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.79%</t>
+          <t>'-0.13%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H8" t="n">
         <v>0.41</v>
@@ -1162,7 +1162,7 @@
         <v>0.44</v>
       </c>
       <c r="O8" t="n">
-        <v>25663286145</v>
+        <v>25977250275</v>
       </c>
       <c r="P8" t="n">
         <v>29750</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45150</v>
+        <v>45300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-0.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="F9" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G9" t="n">
-        <v>2176</v>
+        <v>2222</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>30829490825</v>
+        <v>31058218275</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>257250</v>
+        <v>255750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.81%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>485</v>
       </c>
       <c r="G10" t="n">
-        <v>1574</v>
+        <v>1623</v>
       </c>
       <c r="H10" t="n">
         <v>46.35</v>
@@ -1346,7 +1346,7 @@
         <v>46.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1765543195750</v>
+        <v>1808223567500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>역대급 실적 발표에도 불구하고 주가 부양 실패 및 한국 증시 하락세에 대한 답답함 표출. 미국 이전 희망.</t>
+          <t>역대급 실적 발표에도 불구하고 주가 부양 실패 및 한국 증시 전반의 침체 우려. 정치적 이슈와 맞물린 부정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '실적 발표', '한국 증시']</t>
+          <t>['영업이익', '주가 부양', '한국 증시']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1638000</v>
+        <v>1633000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.56%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G11" t="n">
-        <v>1727</v>
+        <v>1733</v>
       </c>
       <c r="H11" t="n">
         <v>49.52</v>
@@ -1438,7 +1438,7 @@
         <v>49.59</v>
       </c>
       <c r="O11" t="n">
-        <v>2227327980000</v>
+        <v>2309105087500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자회사 상장(쪼개기 상장) 논란 및 정치적 이슈와 연관된 주가 하락에 대한 불만 고조.</t>
+          <t>솔리다임 중복 상장 논란 및 자회사 상장 리스크로 인한 주가 하락. 정치적 이슈와 맞물린 부정적 전망. 최태원 리스크 부각.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['쪼개기 상장', '자회사 상장', '정치적 이슈']</t>
+          <t>['중복 상장', '솔리다임', '최태원 리스크']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16200</v>
+        <v>16170</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-3.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="H12" t="n">
         <v>9.470000000000001</v>
@@ -1530,7 +1530,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>35995005100</v>
+        <v>36880492525</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18270</v>
+        <v>18240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-3.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="H13" t="n">
         <v>27.61</v>
@@ -1622,7 +1622,7 @@
         <v>27.68</v>
       </c>
       <c r="O13" t="n">
-        <v>27681243235</v>
+        <v>28477016420</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>LNG·FLNG '쌍끌이 수주' 소식에도 불구하고 주가 하락 지속. 공매도 및 노조 문제 언급.</t>
+          <t>LNG·FLNG '쌍끌이 수주' 랠리 소식에도 불구하고 주가 하락. 조선주 순환매 기대와 원전 사업 부진, 공매도 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주 랠리', '공매도', '노조']</t>
+          <t>['쌍끌이 수주', '순환매', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>0.16</v>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
         <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H14" t="n">
         <v>1.48</v>
@@ -1714,7 +1714,7 @@
         <v>1.32</v>
       </c>
       <c r="O14" t="n">
-        <v>28415369365</v>
+        <v>28474626480</v>
       </c>
       <c r="P14" t="n">
         <v>2465</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7780</v>
+        <v>7750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.66%</t>
+          <t>'-5.02%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F15" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G15" t="n">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="H15" t="n">
         <v>26.37</v>
@@ -1806,7 +1806,7 @@
         <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>15956456440</v>
+        <v>16596482885</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>수년간의 악재와 부정적 전망 속에서 개인 매수세만 유지. 유상증자 및 상폐 가능성 언급.</t>
+          <t>악재성 뉴스 및 목표가 하향 조정 언급. 차트 회복 불능 및 유상증자 가능성 제기. FLiPP 기술 관련 논쟁.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유상증자', '상폐', '개인 매수세']</t>
+          <t>['목표가 하향', '유상증자', 'FLiPP']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>-0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
         <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="H16" t="n">
         <v>3.37</v>
@@ -1898,7 +1898,7 @@
         <v>3.97</v>
       </c>
       <c r="O16" t="n">
-        <v>63960047610</v>
+        <v>64824972260</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대한광통신의 광통신 테마 부각과 10월 3만원 예상. 하지만 급락 후 오후 급상승 가능성에 대한 기대와 함께 투기적 흐름이 감지됨.</t>
+          <t>3분기 어닝 서프라이즈 발표에도 불구하고 주가 하락. 유튜버 활동 및 공매도 규제 지연에 대한 불만. 17,500원 지지선 붕괴 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신 테마', '급상승', '투기']</t>
+          <t>['어닝 서프라이즈', '공매도 규제', '지지선']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26350</v>
+        <v>26200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.23%</t>
+          <t>'-6.76%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1990,7 +1990,7 @@
         <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>40394648150</v>
+        <v>41304523525</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3965</v>
+        <v>3970</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.14%</t>
+          <t>'-7.03%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2076,13 +2076,13 @@
         <v>4495</v>
       </c>
       <c r="M18" t="n">
-        <v>3950</v>
+        <v>3940</v>
       </c>
       <c r="N18" t="n">
         <v>4.46</v>
       </c>
       <c r="O18" t="n">
-        <v>16168437136</v>
+        <v>16370973771</v>
       </c>
       <c r="P18" t="n">
         <v>5470</v>

--- a/data/trending_integrated_20261012_11.xlsx
+++ b/data/trending_integrated_20261012_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19808390540</v>
+        <v>19818239860</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>131398763510</v>
+        <v>131448501020</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13750</v>
+        <v>13670</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.43%</t>
+          <t>'+22.71%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>143539821205</v>
+        <v>144513249470</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자체 개발 특허 출원 소식 있으나, 외인/기관/기타법인 매도세로 인한 상승 모멘텀 약화. 개미 꼬시기 의혹 제기.</t>
+          <t>금호건설 자체 개발 특허 출원 소식에도 불구하고, 외인, 기관, 기타법인 매도세와 함께 8% 상승은 의미가 없다는 의견.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특허 출원', '매도세', '개미 꼬시기']</t>
+          <t>['특허 출원', '매도세', '주가 흐름']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1624</v>
+        <v>1602</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.09%</t>
+          <t>'+15.50%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>10090890037</v>
+        <v>10207935341</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7920</v>
+        <v>7680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.86%</t>
+          <t>'+8.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>81178793505</v>
+        <v>85400591315</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14630</v>
+        <v>14540</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.18%</t>
+          <t>'+4.53%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>103463676600</v>
+        <v>105024498030</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11325</v>
+        <v>45300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.13%</t>
+          <t>'-0.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>382</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="G8" t="n">
-        <v>66</v>
+        <v>2325</v>
       </c>
       <c r="H8" t="n">
-        <v>0.41</v>
+        <v>13.33</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11340</v>
+        <v>45650</v>
       </c>
       <c r="K8" t="n">
-        <v>11340</v>
+        <v>47550</v>
       </c>
       <c r="L8" t="n">
-        <v>12470</v>
+        <v>47550</v>
       </c>
       <c r="M8" t="n">
-        <v>11120</v>
+        <v>43900</v>
       </c>
       <c r="N8" t="n">
-        <v>0.44</v>
+        <v>13.39</v>
       </c>
       <c r="O8" t="n">
-        <v>25977250275</v>
+        <v>31954483000</v>
       </c>
       <c r="P8" t="n">
-        <v>29750</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>11120</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>46000</v>
+        <v>-115000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>HLB 리보세라닙 간암 1차 치료제 FDA 재승인 서류 제출에 따른 기대감과 함께 공매도 세력에 대한 비판.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['리보세라닙', 'FDA 재승인', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45300</v>
+        <v>11180</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.77%</t>
+          <t>'-1.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>372</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>229</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>2222</v>
+        <v>66</v>
       </c>
       <c r="H9" t="n">
-        <v>13.33</v>
+        <v>0.41</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,183 +1239,183 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>45650</v>
+        <v>11340</v>
       </c>
       <c r="K9" t="n">
-        <v>47550</v>
+        <v>11340</v>
       </c>
       <c r="L9" t="n">
-        <v>47550</v>
+        <v>12470</v>
       </c>
       <c r="M9" t="n">
-        <v>43900</v>
+        <v>11120</v>
       </c>
       <c r="N9" t="n">
-        <v>13.39</v>
+        <v>0.44</v>
       </c>
       <c r="O9" t="n">
-        <v>31058218275</v>
+        <v>26313563900</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>29750</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>11120</v>
       </c>
       <c r="R9" t="n">
-        <v>-115000</v>
+        <v>46000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출에 대한 긍정적 전망. 공매도 세력에 대한 비판과 기대감 고조.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '재승인', '리보세라닙']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>255750</v>
+        <v>2260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-1.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.03</v>
+        <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>485</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>1623</v>
+        <v>101</v>
       </c>
       <c r="H10" t="n">
-        <v>46.35</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>262000</v>
+        <v>2305</v>
       </c>
       <c r="K10" t="n">
-        <v>260000</v>
+        <v>2430</v>
       </c>
       <c r="L10" t="n">
-        <v>262500</v>
+        <v>2445</v>
       </c>
       <c r="M10" t="n">
-        <v>254000</v>
+        <v>2210</v>
       </c>
       <c r="N10" t="n">
-        <v>46.38</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>1808223567500</v>
+        <v>28707932042</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>2465</v>
       </c>
       <c r="Q10" t="n">
-        <v>90200</v>
+        <v>865</v>
       </c>
       <c r="R10" t="n">
-        <v>-416000</v>
+        <v>-442000</v>
       </c>
       <c r="S10" t="n">
-        <v>-81000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>역대급 실적 발표에도 불구하고 주가 부양 실패 및 한국 증시 전반의 침체 우려. 정치적 이슈와 맞물린 부정적 전망.</t>
+          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '한국 증시']</t>
+          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1633000</v>
+        <v>255500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" t="n">
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="G11" t="n">
-        <v>1733</v>
+        <v>1667</v>
       </c>
       <c r="H11" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K11" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L11" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M11" t="n">
-        <v>1605000</v>
+        <v>254000</v>
       </c>
       <c r="N11" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O11" t="n">
-        <v>2309105087500</v>
+        <v>1853710551250</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R11" t="n">
-        <v>-276000</v>
+        <v>-416000</v>
       </c>
       <c r="S11" t="n">
-        <v>14000</v>
+        <v>-81000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>솔리다임 중복 상장 논란 및 자회사 상장 리스크로 인한 주가 하락. 정치적 이슈와 맞물린 부정적 전망. 최태원 리스크 부각.</t>
+          <t>역대급 실적에도 불구하고 주가 부양 안 된다는 비판과 함께 한국 증시 하락세에 대한 불만.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['중복 상장', '솔리다임', '최태원 리스크']</t>
+          <t>['영업이익', '주가 부양', '한국 증시']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16170</v>
+        <v>1634000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.00%</t>
+          <t>'-2.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>114</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>502</v>
       </c>
       <c r="G12" t="n">
-        <v>443</v>
+        <v>1749</v>
       </c>
       <c r="H12" t="n">
-        <v>9.470000000000001</v>
+        <v>49.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16670</v>
+        <v>1681000</v>
       </c>
       <c r="K12" t="n">
-        <v>16500</v>
+        <v>1640000</v>
       </c>
       <c r="L12" t="n">
-        <v>16870</v>
+        <v>1653000</v>
       </c>
       <c r="M12" t="n">
-        <v>16130</v>
+        <v>1605000</v>
       </c>
       <c r="N12" t="n">
-        <v>9.460000000000001</v>
+        <v>49.59</v>
       </c>
       <c r="O12" t="n">
-        <v>36880492525</v>
+        <v>2368700644500</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>367000</v>
+        <v>-276000</v>
       </c>
       <c r="S12" t="n">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주주 연대의 활동 언급 및 '뱅크런' 등 부정적 용어 반복 사용. 목표가 3만원 언급.</t>
+          <t>SK하이닉스 주가 하락과 자회사 솔리다임 중복 상장 논란에 대한 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주주연대', '뱅크런', '목표가']</t>
+          <t>['주가 하락', '중복 상장', '솔리다임']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18240</v>
+        <v>16140</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.29%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>271</v>
+        <v>463</v>
       </c>
       <c r="H13" t="n">
-        <v>27.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18860</v>
+        <v>16670</v>
       </c>
       <c r="K13" t="n">
-        <v>18690</v>
+        <v>16500</v>
       </c>
       <c r="L13" t="n">
-        <v>18760</v>
+        <v>16870</v>
       </c>
       <c r="M13" t="n">
-        <v>18100</v>
+        <v>16130</v>
       </c>
       <c r="N13" t="n">
-        <v>27.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>28477016420</v>
+        <v>37805347300</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>18100</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>29000</v>
+        <v>367000</v>
       </c>
       <c r="S13" t="n">
-        <v>23000</v>
+        <v>17000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>LNG·FLNG '쌍끌이 수주' 랠리 소식에도 불구하고 주가 하락. 조선주 순환매 기대와 원전 사업 부진, 공매도 우려.</t>
+          <t>대우건설 주주들에게 범죄 짓거리 중단을 요구하는 반복적인 게시글.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['쌍끌이 수주', '순환매', '공매도']</t>
+          <t>['주주 연대', '범죄 짓거리', '대차 해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,130 +1660,130 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2225</v>
+        <v>18220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.47%</t>
+          <t>'-3.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>92</v>
+        <v>284</v>
       </c>
       <c r="H14" t="n">
-        <v>1.48</v>
+        <v>27.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2305</v>
+        <v>18860</v>
       </c>
       <c r="K14" t="n">
-        <v>2430</v>
+        <v>18690</v>
       </c>
       <c r="L14" t="n">
-        <v>2445</v>
+        <v>18760</v>
       </c>
       <c r="M14" t="n">
-        <v>2210</v>
+        <v>18100</v>
       </c>
       <c r="N14" t="n">
-        <v>1.32</v>
+        <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>28474626480</v>
+        <v>30246051470</v>
       </c>
       <c r="P14" t="n">
-        <v>2465</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>865</v>
+        <v>18100</v>
       </c>
       <c r="R14" t="n">
-        <v>-442000</v>
+        <v>29000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
+          <t>삼성중공업의 LNG·FLNG 쌍끌이 수주 랠리에도 불구하고, 국내 증시 하락세와 주가 폭락에 대한 불안감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
+          <t>['수주 랠리', '국내 증시', '주가 폭락']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7750</v>
+        <v>4065</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.02%</t>
+          <t>'-4.80%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.01</v>
+        <v>-2.94</v>
       </c>
       <c r="E15" t="n">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>530</v>
+        <v>56</v>
       </c>
       <c r="H15" t="n">
-        <v>26.37</v>
+        <v>1.52</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,130 +1791,130 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8160</v>
+        <v>4270</v>
       </c>
       <c r="K15" t="n">
-        <v>8070</v>
+        <v>4150</v>
       </c>
       <c r="L15" t="n">
-        <v>8110</v>
+        <v>4495</v>
       </c>
       <c r="M15" t="n">
-        <v>7730</v>
+        <v>3940</v>
       </c>
       <c r="N15" t="n">
-        <v>26.38</v>
+        <v>4.46</v>
       </c>
       <c r="O15" t="n">
-        <v>16596482885</v>
+        <v>16667513352</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>5470</v>
       </c>
       <c r="Q15" t="n">
-        <v>7730</v>
+        <v>2810</v>
       </c>
       <c r="R15" t="n">
-        <v>-595000</v>
+        <v>-92000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>악재성 뉴스 및 목표가 하향 조정 언급. 차트 회복 불능 및 유상증자 가능성 제기. FLiPP 기술 관련 논쟁.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['목표가 하향', '유상증자', 'FLiPP']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16000</v>
+        <v>7730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.72%</t>
+          <t>'-5.27%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.6</v>
+        <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>401</v>
+        <v>561</v>
       </c>
       <c r="H16" t="n">
-        <v>3.37</v>
+        <v>26.37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16970</v>
+        <v>8160</v>
       </c>
       <c r="K16" t="n">
-        <v>17030</v>
+        <v>8070</v>
       </c>
       <c r="L16" t="n">
-        <v>17400</v>
+        <v>8110</v>
       </c>
       <c r="M16" t="n">
-        <v>15650</v>
+        <v>7710</v>
       </c>
       <c r="N16" t="n">
-        <v>3.97</v>
+        <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>64824972260</v>
+        <v>17734498540</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>7710</v>
       </c>
       <c r="R16" t="n">
-        <v>59000</v>
+        <v>-595000</v>
       </c>
       <c r="S16" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 발표에도 불구하고 주가 하락. 유튜버 활동 및 공매도 규제 지연에 대한 불만. 17,500원 지지선 붕괴 우려.</t>
+          <t>악재성 뉴스 및 목표가 하향 조정 언급. 차트 회복 불능 및 유상증자 가능성 제기. FLiPP 기술 관련 논쟁.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '공매도 규제', '지지선']</t>
+          <t>['목표가 하향', '유상증자', 'FLiPP']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,130 +1936,130 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26200</v>
+        <v>15980</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.76%</t>
+          <t>'-5.83%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>54</v>
+        <v>405</v>
       </c>
       <c r="H17" t="n">
-        <v>9.460000000000001</v>
+        <v>3.37</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>28100</v>
+        <v>16970</v>
       </c>
       <c r="K17" t="n">
-        <v>27600</v>
+        <v>17030</v>
       </c>
       <c r="L17" t="n">
-        <v>27800</v>
+        <v>17400</v>
       </c>
       <c r="M17" t="n">
-        <v>26050</v>
+        <v>15650</v>
       </c>
       <c r="N17" t="n">
-        <v>10.02</v>
+        <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>41304523525</v>
+        <v>65537066265</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>15960</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-9000</v>
+        <v>59000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
+          <t>3분기 어닝 서프라이즈 발표에도 불구하고 주가 하락. 유튜버 활동 및 공매도 규제 지연에 대한 불만. 17,500원 지지선 붕괴 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['경영진 부진', '기술유출', '실적 우려']</t>
+          <t>['어닝 서프라이즈', '공매도 규제', '지지선']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3970</v>
+        <v>26150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.03%</t>
+          <t>'-6.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-2.94</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H18" t="n">
-        <v>1.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4270</v>
+        <v>28100</v>
       </c>
       <c r="K18" t="n">
-        <v>4150</v>
+        <v>27600</v>
       </c>
       <c r="L18" t="n">
-        <v>4495</v>
+        <v>27800</v>
       </c>
       <c r="M18" t="n">
-        <v>3940</v>
+        <v>26050</v>
       </c>
       <c r="N18" t="n">
-        <v>4.46</v>
+        <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>16370973771</v>
+        <v>41893702650</v>
       </c>
       <c r="P18" t="n">
-        <v>5470</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>2810</v>
+        <v>15960</v>
       </c>
       <c r="R18" t="n">
-        <v>-92000</v>
+        <v>-9000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
+          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['코로나19', '모더나', '단기 모멘텀']</t>
+          <t>['경영진 부진', '기술유출', '실적 우려']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
